--- a/Result/profitability/1474.xlsx
+++ b/Result/profitability/1474.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,7 +672,7 @@
         <v>0.04499999999999997</v>
       </c>
       <c r="N2" t="n">
-        <v>10.16875</v>
+        <v>10.2225</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05374999999999998</v>
+        <v>0.04499999999999998</v>
       </c>
       <c r="N3" t="n">
-        <v>9.827500000000001</v>
+        <v>9.94</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,13 +899,13 @@
         <v>0.03</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05124999999999998</v>
+        <v>0.02624999999999997</v>
       </c>
       <c r="N4" t="n">
-        <v>9.449999999999999</v>
+        <v>9.025</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02999999999999998</v>
+        <v>0.03249999999999998</v>
       </c>
       <c r="N5" t="n">
-        <v>8.37125</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.04374999999999998</v>
+        <v>0.02249999999999998</v>
       </c>
       <c r="N6" t="n">
-        <v>7.96625</v>
+        <v>7.87375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02499999999999998</v>
+        <v>0.01624999999999998</v>
       </c>
       <c r="N7" t="n">
-        <v>8.01375</v>
+        <v>8.09</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.05</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02499999999999998</v>
+        <v>0.01124999999999998</v>
       </c>
       <c r="N8" t="n">
-        <v>8.34</v>
+        <v>8.22125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1650,7 +1650,7 @@
         <v>0.04624999999999998</v>
       </c>
       <c r="N10" t="n">
-        <v>8.7925</v>
+        <v>8.792499999999999</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1474</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>679</v>
+      </c>
+      <c r="D75" t="n">
+        <v>612</v>
+      </c>
+      <c r="E75" t="n">
+        <v>68</v>
+      </c>
+      <c r="F75" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>8</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.05499999999999997</v>
+      </c>
+      <c r="N75" t="n">
+        <v>10.595</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.222222222222222</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.9500000000000011</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.08715596330275244</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.010000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1680602006688965</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
